--- a/Daily_Team_Stats.xlsx
+++ b/Daily_Team_Stats.xlsx
@@ -18,10 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="86">
-  <si>
-    <t>ABFF Client Support</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="84">
   <si>
     <t>Adjara Sport Client Support</t>
   </si>
@@ -177,9 +174,6 @@
   </si>
   <si>
     <t>WWE Client Support</t>
-  </si>
-  <si>
-    <t>ABFF Play</t>
   </si>
   <si>
     <t>BroadwayHD</t>
@@ -607,10 +601,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BA2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:53">
+    <row r="1" spans="1:52">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -767,130 +761,127 @@
       <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="2" spans="1:53">
+    <row r="2" spans="1:52">
       <c r="A2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
       <c r="AN2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -911,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AU2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2">
         <v>0</v>
@@ -926,9 +917,6 @@
         <v>0</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
         <v>0</v>
       </c>
     </row>
@@ -939,10 +927,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BA2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:53">
+    <row r="1" spans="1:52">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1099,151 +1087,148 @@
       <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="2" spans="1:53">
+    <row r="2" spans="1:52">
       <c r="A2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="B2">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C2">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D2">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>3</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>6</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>7</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
         <v>2</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>2</v>
-      </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>3</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>35</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
         <v>4</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>1</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>39</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>1</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>1</v>
       </c>
       <c r="AT2">
         <v>2</v>
       </c>
       <c r="AU2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV2">
         <v>0</v>
@@ -1252,15 +1237,12 @@
         <v>0</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ2">
-        <v>1</v>
-      </c>
-      <c r="BA2">
         <v>1</v>
       </c>
     </row>
@@ -1271,146 +1253,143 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>59</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>61</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>62</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>63</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>64</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>65</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>66</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>67</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>68</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>69</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>70</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>71</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>72</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>73</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>74</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>75</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>76</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>77</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>78</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>79</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>80</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>81</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>82</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>83</v>
       </c>
-      <c r="AF1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>85</v>
-      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:32">
       <c r="A2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="L2">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -1419,49 +1398,49 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="V2">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA2">
-        <v>1428</v>
+        <v>134</v>
       </c>
       <c r="AB2">
-        <v>423</v>
+        <v>1</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1470,10 +1449,7 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1483,194 +1459,191 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>59</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>61</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>62</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>63</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>64</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>65</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>66</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>67</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>68</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>69</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>70</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>71</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>72</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>73</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>74</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>75</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>76</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>77</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>78</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>79</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>80</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>81</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>82</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>83</v>
       </c>
-      <c r="AF1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>85</v>
-      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:32">
       <c r="A2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>13</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>66</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>8</v>
+      </c>
+      <c r="X2">
+        <v>8</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>11</v>
+      </c>
+      <c r="AA2">
         <v>10</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>7</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>3</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>1</v>
-      </c>
-      <c r="V2">
-        <v>18</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>26</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>19</v>
-      </c>
       <c r="AB2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1679,13 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1700,27 +1670,27 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1729,13 +1699,13 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>520</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Team_Stats.xlsx
+++ b/Daily_Team_Stats.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="77">
   <si>
     <t>Adjara Sport Client Support</t>
   </si>
@@ -44,15 +44,9 @@
     <t>Carlisle United Client Support</t>
   </si>
   <si>
-    <t>Core Sports Client Support</t>
-  </si>
-  <si>
     <t>Dallas Mavericks Client Support</t>
   </si>
   <si>
-    <t>ELF Client Support</t>
-  </si>
-  <si>
     <t>Endeavor Streaming Privacy</t>
   </si>
   <si>
@@ -161,12 +155,6 @@
     <t>UFC Fight Pass Brasil Client Support</t>
   </si>
   <si>
-    <t>Univision Now Client Support</t>
-  </si>
-  <si>
-    <t>USGA Client Support</t>
-  </si>
-  <si>
     <t>WNBA League Pass Client Support</t>
   </si>
   <si>
@@ -188,9 +176,6 @@
     <t>Dice Support Tickets</t>
   </si>
   <si>
-    <t>European League of Football</t>
-  </si>
-  <si>
     <t>EuroLeague TV</t>
   </si>
   <si>
@@ -255,12 +240,6 @@
   </si>
   <si>
     <t>UFC Fight Pass Brasil</t>
-  </si>
-  <si>
-    <t>Univision Now</t>
-  </si>
-  <si>
-    <t>Univision TVE</t>
   </si>
   <si>
     <t>WNBA</t>
@@ -601,10 +580,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="1:48">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -749,175 +728,151 @@
       <c r="AV1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>51</v>
-      </c>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="1:48">
       <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>4</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>1</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>1</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>2</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
       <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -927,10 +882,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="1:48">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1075,28 +1030,16 @@
       <c r="AV1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>51</v>
-      </c>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="1:48">
       <c r="A2">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1105,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -1114,97 +1057,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>1</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
+      <c r="T2">
         <v>1</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>4</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>6</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>3</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
         <v>1</v>
       </c>
-      <c r="V2">
+      <c r="AJ2">
         <v>1</v>
       </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>3</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>6</v>
-      </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>7</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>2</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
       <c r="AK2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AL2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -1216,33 +1159,21 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR2">
         <v>1</v>
       </c>
       <c r="AS2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
         <v>2</v>
       </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
       <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>1</v>
-      </c>
-      <c r="AY2">
-        <v>2</v>
-      </c>
-      <c r="AZ2">
         <v>1</v>
       </c>
     </row>
@@ -1253,203 +1184,185 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>59</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>60</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>61</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>62</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>63</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>64</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
         <v>65</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" t="s">
         <v>66</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" t="s">
         <v>67</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
         <v>68</v>
       </c>
-      <c r="R1" t="s">
+      <c r="V1" t="s">
         <v>69</v>
       </c>
-      <c r="S1" t="s">
+      <c r="W1" t="s">
         <v>70</v>
       </c>
-      <c r="T1" t="s">
+      <c r="X1" t="s">
         <v>71</v>
       </c>
-      <c r="U1" t="s">
+      <c r="Y1" t="s">
         <v>72</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Z1" t="s">
         <v>73</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AA1" t="s">
         <v>74</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AB1" t="s">
         <v>75</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>76</v>
       </c>
-      <c r="Z1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>83</v>
-      </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:29">
       <c r="A2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F2">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>274</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>29</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>3</v>
+      </c>
+      <c r="R2">
+        <v>3</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>60</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>4</v>
+      </c>
+      <c r="W2">
+        <v>6</v>
+      </c>
+      <c r="X2">
         <v>2</v>
       </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>264</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>9</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>4</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>80</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>22</v>
-      </c>
-      <c r="X2">
-        <v>6</v>
-      </c>
       <c r="Y2">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="Z2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="AA2">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>1</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1459,203 +1372,185 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>59</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>60</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>61</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>62</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>63</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>64</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
         <v>65</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" t="s">
         <v>66</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" t="s">
         <v>67</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
         <v>68</v>
       </c>
-      <c r="R1" t="s">
+      <c r="V1" t="s">
         <v>69</v>
       </c>
-      <c r="S1" t="s">
+      <c r="W1" t="s">
         <v>70</v>
       </c>
-      <c r="T1" t="s">
+      <c r="X1" t="s">
         <v>71</v>
       </c>
-      <c r="U1" t="s">
+      <c r="Y1" t="s">
         <v>72</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Z1" t="s">
         <v>73</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AA1" t="s">
         <v>74</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AB1" t="s">
         <v>75</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>76</v>
       </c>
-      <c r="Z1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>83</v>
-      </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:29">
       <c r="A2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>26</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>42</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>4</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>33</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>6</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>13</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="U2">
-        <v>66</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>8</v>
-      </c>
-      <c r="X2">
-        <v>8</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>11</v>
-      </c>
-      <c r="AA2">
-        <v>10</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>1</v>
-      </c>
-      <c r="AF2">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1665,47 +1560,41 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
         <v>57</v>
       </c>
-      <c r="B1" t="s">
-        <v>62</v>
-      </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>40</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>15</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
       <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
